--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3397" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3399" uniqueCount="343">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -529,10 +529,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -4711,7 +4714,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>166</v>
       </c>
@@ -4730,7 +4733,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4741,8 +4744,12 @@
       <c r="K33" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
+      <c r="L33" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4812,10 +4819,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4829,7 +4836,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4838,13 +4845,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4895,7 +4902,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4915,10 +4922,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5014,12 +5021,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5029,13 +5036,13 @@
         <v>62</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5048,7 +5055,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5060,7 +5067,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -5099,7 +5106,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5117,28 +5124,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5151,7 +5158,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5163,7 +5170,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5202,7 +5209,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5222,17 +5229,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5254,7 +5261,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5266,7 +5273,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5305,7 +5312,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5325,17 +5332,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5357,7 +5364,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5408,7 +5415,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5426,28 +5433,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5460,7 +5467,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5472,7 +5479,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5511,7 +5518,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5531,10 +5538,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5557,11 +5564,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5612,7 +5619,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5632,10 +5639,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5662,7 +5669,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5713,7 +5720,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5733,17 +5740,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5761,11 +5768,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5816,7 +5823,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5836,17 +5843,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5864,11 +5871,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5919,7 +5926,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5939,17 +5946,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5967,11 +5974,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6022,7 +6029,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6042,10 +6049,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6059,7 +6066,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -6068,13 +6075,13 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6125,7 +6132,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6145,10 +6152,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6162,7 +6169,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6171,13 +6178,13 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6228,7 +6235,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6248,10 +6255,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6274,7 +6281,7 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6327,7 +6334,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6347,10 +6354,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6406,25 +6413,25 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6444,10 +6451,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6470,7 +6477,7 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6523,7 +6530,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6543,10 +6550,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6569,7 +6576,7 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6622,7 +6629,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6642,10 +6649,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6668,7 +6675,7 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -6721,7 +6728,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6741,10 +6748,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6752,13 +6759,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6767,7 +6774,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6808,7 +6815,7 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -6818,7 +6825,7 @@
         <v>124</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6838,13 +6845,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>74</v>
@@ -6866,7 +6873,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6919,7 +6926,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6939,10 +6946,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7040,10 +7047,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7141,10 +7148,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7242,10 +7249,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7343,10 +7350,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7446,10 +7453,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7549,10 +7556,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7652,10 +7659,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7755,10 +7762,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7856,10 +7863,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7889,7 +7896,7 @@
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
@@ -7915,7 +7922,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -7933,7 +7940,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7953,10 +7960,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7990,7 +7997,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>74</v>
@@ -8032,7 +8039,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8052,10 +8059,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8078,7 +8085,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8131,7 +8138,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8151,10 +8158,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8177,7 +8184,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8230,7 +8237,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8250,10 +8257,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8276,10 +8283,10 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -8331,7 +8338,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8351,10 +8358,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8377,7 +8384,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8430,7 +8437,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8450,10 +8457,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8476,7 +8483,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8529,7 +8536,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8549,10 +8556,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8575,7 +8582,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8628,7 +8635,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8648,10 +8655,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8674,7 +8681,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8727,7 +8734,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8747,10 +8754,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8773,7 +8780,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8826,7 +8833,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8846,10 +8853,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8872,7 +8879,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8925,7 +8932,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8945,13 +8952,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>74</v>
@@ -8973,7 +8980,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9026,7 +9033,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9046,10 +9053,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9147,10 +9154,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9248,10 +9255,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9349,10 +9356,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9450,10 +9457,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9553,10 +9560,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9656,10 +9663,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9759,10 +9766,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9862,10 +9869,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9963,10 +9970,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9996,7 +10003,7 @@
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
@@ -10022,7 +10029,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -10040,7 +10047,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10060,10 +10067,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10097,7 +10104,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>74</v>
@@ -10139,7 +10146,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10159,10 +10166,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10185,7 +10192,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10238,7 +10245,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10258,10 +10265,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10284,7 +10291,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10337,7 +10344,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10357,10 +10364,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10383,10 +10390,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -10438,7 +10445,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10458,10 +10465,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10484,7 +10491,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10537,7 +10544,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10557,10 +10564,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10583,7 +10590,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10636,7 +10643,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10656,10 +10663,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10682,7 +10689,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10735,7 +10742,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10755,10 +10762,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10781,7 +10788,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10834,7 +10841,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10854,10 +10861,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10880,7 +10887,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10933,7 +10940,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -10953,10 +10960,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -10979,7 +10986,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11032,7 +11039,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11052,10 +11059,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11078,7 +11085,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11131,7 +11138,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11151,10 +11158,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11252,10 +11259,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11353,10 +11360,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11454,10 +11461,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11555,10 +11562,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11658,10 +11665,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11761,10 +11768,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11864,10 +11871,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -11967,10 +11974,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12068,10 +12075,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12098,7 +12105,7 @@
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12107,7 +12114,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>74</v>
@@ -12149,7 +12156,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12169,10 +12176,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12206,7 +12213,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>74</v>
@@ -12248,7 +12255,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12268,10 +12275,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12294,7 +12301,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12347,7 +12354,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-raison-de-la-recommandation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
